--- a/data/trans_bre/P0902-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P0902-Edad-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 4,36</t>
+          <t>-0,17; 4,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 4,4</t>
+          <t>-0,61; 4,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 3,45</t>
+          <t>-0,91; 3,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 9,07</t>
+          <t>1,39; 7,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 330,54</t>
+          <t>-13,52; 305,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,39; 250,72</t>
+          <t>-22,45; 268,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-44,35; 356,15</t>
+          <t>-39,72; 364,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,91; 6,82</t>
+          <t>2,14; 6,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 4,19</t>
+          <t>-0,54; 4,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 4,27</t>
+          <t>-0,79; 4,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 0,78</t>
+          <t>-6,78; 0,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>49,36; 375,5</t>
+          <t>58,0; 382,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-17,39; 181,31</t>
+          <t>-15,31; 191,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,36; 182,5</t>
+          <t>-18,17; 181,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-70,83; 17,1</t>
+          <t>-66,78; 16,73</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 6,64</t>
+          <t>0,83; 6,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,0; 8,31</t>
+          <t>1,98; 8,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 6,23</t>
+          <t>0,9; 6,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 6,6</t>
+          <t>0,24; 6,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,74; 199,25</t>
+          <t>12,01; 179,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,61; 180,36</t>
+          <t>26,12; 169,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,11; 202,3</t>
+          <t>13,82; 194,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,86; 132,01</t>
+          <t>2,5; 130,26</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,35; 9,65</t>
+          <t>2,38; 9,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,04; 11,59</t>
+          <t>3,49; 11,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 6,75</t>
+          <t>0,1; 7,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 13,47</t>
+          <t>0,28; 12,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,2; 178,69</t>
+          <t>25,73; 176,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,84; 171,83</t>
+          <t>33,94; 175,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 91,57</t>
+          <t>0,69; 92,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,79; 286,76</t>
+          <t>1,23; 254,59</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 6,95</t>
+          <t>-2,87; 6,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,55; 17,55</t>
+          <t>6,7; 17,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,2; 16,82</t>
+          <t>6,88; 16,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 7,73</t>
+          <t>-0,92; 7,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-19,79; 63,08</t>
+          <t>-18,83; 62,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,32; 129,75</t>
+          <t>37,81; 136,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,74; 169,99</t>
+          <t>47,56; 176,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 48,23</t>
+          <t>-4,15; 42,84</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,31; 19,29</t>
+          <t>6,56; 19,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,89; 20,81</t>
+          <t>5,8; 20,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,96; 22,58</t>
+          <t>8,68; 21,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,29; 13,04</t>
+          <t>-10,33; 12,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30,92; 145,44</t>
+          <t>33,76; 145,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,22; 106,68</t>
+          <t>21,36; 110,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>49,79; 167,04</t>
+          <t>44,63; 166,82</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-54,83; 81,99</t>
+          <t>-54,34; 81,06</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 16,72</t>
+          <t>-0,03; 17,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,81; 24,19</t>
+          <t>6,7; 23,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,85; 28,39</t>
+          <t>12,45; 28,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16,69; 27,87</t>
+          <t>16,66; 27,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 59,47</t>
+          <t>0,54; 58,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,69; 62,15</t>
+          <t>13,57; 61,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,22; 97,48</t>
+          <t>33,92; 100,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>46,4; 96,9</t>
+          <t>44,6; 95,96</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,88; 7,88</t>
+          <t>4,93; 8,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,25; 10,76</t>
+          <t>7,06; 10,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,81; 10,18</t>
+          <t>6,81; 10,06</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,89; 9,04</t>
+          <t>3,09; 9,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>55,09; 104,62</t>
+          <t>56,61; 108,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>62,05; 107,88</t>
+          <t>59,77; 104,4</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>68,18; 119,32</t>
+          <t>66,81; 116,04</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>26,66; 91,91</t>
+          <t>26,11; 93,42</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P0902-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P0902-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,91</t>
+          <t>4,89</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 4,25</t>
+          <t>-0,08; 4,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 4,15</t>
+          <t>-0,63; 4,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 3,33</t>
+          <t>-0,93; 3,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 7,78</t>
+          <t>2,26; 9,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,52; 305,35</t>
+          <t>-7,22; 351,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-22,45; 268,07</t>
+          <t>-19,54; 247,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-39,72; 364,01</t>
+          <t>-41,48; 375,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,54</t>
+          <t>-1,61</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-35,58%</t>
+          <t>-23,91%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,14; 6,86</t>
+          <t>2,18; 6,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 4,18</t>
+          <t>-0,45; 4,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 4,25</t>
+          <t>-0,7; 4,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 0,71</t>
+          <t>-5,17; 1,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>58,0; 382,37</t>
+          <t>54,24; 368,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-15,31; 191,71</t>
+          <t>-15,38; 178,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-18,17; 181,67</t>
+          <t>-16,13; 179,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-66,78; 16,73</t>
+          <t>-58,8; 44,75</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,5</t>
+          <t>3,94</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>64,97%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 6,39</t>
+          <t>1,02; 6,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,98; 8,15</t>
+          <t>2,09; 8,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 6,06</t>
+          <t>0,92; 6,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 6,68</t>
+          <t>1,25; 6,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,01; 179,27</t>
+          <t>15,23; 182,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,12; 169,01</t>
+          <t>22,92; 169,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,82; 194,76</t>
+          <t>12,55; 189,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,5; 130,26</t>
+          <t>14,46; 148,52</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,04</t>
+          <t>1,61</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>12,38%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,38; 9,48</t>
+          <t>2,33; 9,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,49; 11,16</t>
+          <t>3,87; 11,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 7,04</t>
+          <t>0,17; 7,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 12,13</t>
+          <t>-2,04; 4,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,73; 176,72</t>
+          <t>26,41; 175,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,94; 175,47</t>
+          <t>35,92; 170,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 92,83</t>
+          <t>1,36; 92,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 254,59</t>
+          <t>-13,55; 44,13</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,34</t>
+          <t>4,55</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>24,63%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 6,76</t>
+          <t>-3,36; 6,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,7; 17,46</t>
+          <t>6,02; 17,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,88; 16,67</t>
+          <t>6,37; 16,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 7,14</t>
+          <t>0,55; 8,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,83; 62,81</t>
+          <t>-21,63; 60,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,81; 136,07</t>
+          <t>32,0; 132,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,56; 176,8</t>
+          <t>41,74; 167,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 42,84</t>
+          <t>2,3; 51,22</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,03</t>
+          <t>12,2</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>75,08%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,56; 19,1</t>
+          <t>6,53; 19,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,8; 20,62</t>
+          <t>6,0; 20,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,68; 21,94</t>
+          <t>9,84; 22,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,33; 12,8</t>
+          <t>7,38; 16,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33,76; 145,16</t>
+          <t>31,2; 136,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,36; 110,37</t>
+          <t>20,49; 101,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44,63; 166,82</t>
+          <t>50,07; 172,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-54,34; 81,06</t>
+          <t>39,39; 120,62</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22,32</t>
+          <t>22,55</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,3%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 17,11</t>
+          <t>-0,36; 17,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,7; 23,59</t>
+          <t>7,28; 24,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,45; 28,32</t>
+          <t>12,5; 28,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16,66; 27,74</t>
+          <t>16,08; 28,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 58,41</t>
+          <t>-0,93; 61,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,57; 61,22</t>
+          <t>14,63; 63,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,92; 100,52</t>
+          <t>33,26; 98,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>44,6; 95,96</t>
+          <t>45,0; 100,9</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6,28</t>
+          <t>7,2</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>57,72%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,93; 8,03</t>
+          <t>4,94; 8,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,06; 10,66</t>
+          <t>7,22; 10,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,81; 10,06</t>
+          <t>6,71; 10,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,09; 9,1</t>
+          <t>5,68; 8,73</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>56,61; 108,33</t>
+          <t>55,91; 108,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>59,77; 104,4</t>
+          <t>61,6; 105,61</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>66,81; 116,04</t>
+          <t>67,2; 119,04</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>26,11; 93,42</t>
+          <t>42,25; 73,94</t>
         </is>
       </c>
     </row>
